--- a/verificables revisión sistemática/S8_recuperacion_texto_completo.xlsx
+++ b/verificables revisión sistemática/S8_recuperacion_texto_completo.xlsx
@@ -689,7 +689,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-08-26</t>
+          <t>Generado el 2026-08-28</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S8_recuperacion_texto_completo.xlsx
+++ b/verificables revisión sistemática/S8_recuperacion_texto_completo.xlsx
@@ -689,7 +689,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-08-28</t>
+          <t>Generado el 2026-08-31</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S8_recuperacion_texto_completo.xlsx
+++ b/verificables revisión sistemática/S8_recuperacion_texto_completo.xlsx
@@ -689,7 +689,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-08-31</t>
+          <t>Generado el 2026-09-01</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S8_recuperacion_texto_completo.xlsx
+++ b/verificables revisión sistemática/S8_recuperacion_texto_completo.xlsx
@@ -689,7 +689,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-01</t>
+          <t>Generado el 2026-09-02</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S8_recuperacion_texto_completo.xlsx
+++ b/verificables revisión sistemática/S8_recuperacion_texto_completo.xlsx
@@ -689,7 +689,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-02</t>
+          <t>Generado el 2026-09-14</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S8_recuperacion_texto_completo.xlsx
+++ b/verificables revisión sistemática/S8_recuperacion_texto_completo.xlsx
@@ -689,7 +689,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-14</t>
+          <t>Generado el 2026-09-15</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S8_recuperacion_texto_completo.xlsx
+++ b/verificables revisión sistemática/S8_recuperacion_texto_completo.xlsx
@@ -689,7 +689,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-15</t>
+          <t>Generado el 2026-09-16</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S8_recuperacion_texto_completo.xlsx
+++ b/verificables revisión sistemática/S8_recuperacion_texto_completo.xlsx
@@ -689,7 +689,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-16</t>
+          <t>Generado el 2026-09-22</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S8_recuperacion_texto_completo.xlsx
+++ b/verificables revisión sistemática/S8_recuperacion_texto_completo.xlsx
@@ -689,7 +689,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-22</t>
+          <t>Generado el 2026-09-23</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S8_recuperacion_texto_completo.xlsx
+++ b/verificables revisión sistemática/S8_recuperacion_texto_completo.xlsx
@@ -689,7 +689,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-23</t>
+          <t>Generado el 2026-10-03</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S8_recuperacion_texto_completo.xlsx
+++ b/verificables revisión sistemática/S8_recuperacion_texto_completo.xlsx
@@ -689,7 +689,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-03</t>
+          <t>Generado el 2026-10-06</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S8_recuperacion_texto_completo.xlsx
+++ b/verificables revisión sistemática/S8_recuperacion_texto_completo.xlsx
@@ -689,7 +689,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-06</t>
+          <t>Generado el 2026-10-07</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S8_recuperacion_texto_completo.xlsx
+++ b/verificables revisión sistemática/S8_recuperacion_texto_completo.xlsx
@@ -689,7 +689,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-07</t>
+          <t>Generado el 2026-10-08</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S8_recuperacion_texto_completo.xlsx
+++ b/verificables revisión sistemática/S8_recuperacion_texto_completo.xlsx
@@ -689,7 +689,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-08</t>
+          <t>Generado el 2026-10-12</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S8_recuperacion_texto_completo.xlsx
+++ b/verificables revisión sistemática/S8_recuperacion_texto_completo.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,6 +41,10 @@
       <b val="1"/>
       <color rgb="001F4E79"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -89,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -100,11 +104,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -472,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -499,7 +506,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Cómo se localizó cada texto completo, o por qué no se pudo.</t>
+          <t>La vía de recuperación resuelta para cada informe sin DOI editorial (resúmenes de congreso, fichas de registro y algunos artículos): el identificador que se resolvió y cómo. No es el registro de los intentos de obtener cada texto completo.</t>
         </is>
       </c>
     </row>
@@ -516,180 +523,187 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Sección 3.2. Explica el sesgo de recuperación que el artículo mide.</t>
+          <t>Sección 3.2.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Las secciones y tablas que se citan son las del informe extendido (manuscrito maestro). En el manuscrito preparado para la revista las secciones no van numeradas.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Cuántas filas</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>45 filas de datos</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
-    </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Qué significa cada columna</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Orden</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>columna interna: orden</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Identificador del informe</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>columna interna: record_id</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Tipo de informe</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>columna interna: tipo</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>Identificador resuelto</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>columna interna: identificador_resuelto</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Cómo se localizó</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>columna interna: via</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Nota</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>columna interna: nota</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>Duplicado interno</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>columna interna: duplicado_interno</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>Título</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>columna interna: titulo</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>Revista</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>columna interna: revista</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>Año</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>columna interna: anio</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>Fuentes que lo aportaron</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>columna interna: fuentes</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>El CSV con los nombres internos acompaña a este fichero: es la copia reproducible.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>Generado el 2026-10-12</t>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>Generado el 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -721,57 +735,57 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Orden</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>Identificador del informe</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>Tipo de informe</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>Identificador resuelto</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>Cómo se localizó</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>Nota</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>Duplicado interno</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>Título</t>
         </is>
       </c>
-      <c r="I1" s="8" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>Revista</t>
         </is>
       </c>
-      <c r="J1" s="8" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>Año</t>
         </is>
       </c>
-      <c r="K1" s="8" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>Fuentes que lo aportaron</t>
         </is>

--- a/verificables revisión sistemática/S8_recuperacion_texto_completo.xlsx
+++ b/verificables revisión sistemática/S8_recuperacion_texto_completo.xlsx
@@ -703,7 +703,7 @@
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-14</t>
+          <t>Generado el 2026-10-15</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S8_recuperacion_texto_completo.xlsx
+++ b/verificables revisión sistemática/S8_recuperacion_texto_completo.xlsx
@@ -703,7 +703,7 @@
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-15</t>
+          <t>Generado el 2026-10-19</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S8_recuperacion_texto_completo.xlsx
+++ b/verificables revisión sistemática/S8_recuperacion_texto_completo.xlsx
@@ -506,7 +506,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>La vía de recuperación resuelta para cada informe sin DOI editorial (resúmenes de congreso, fichas de registro y algunos artículos): el identificador que se resolvió y cómo. No es el registro de los intentos de obtener cada texto completo.</t>
+          <t>La vía de recuperación resuelta para cada informe sin DOI editorial (resúmenes de congreso, fichas de registro y algunos artículos): el identificador que se resolvió y cómo. No es el registro de los intentos de obtener cada texto completo. Tiene 45 filas: los 43 informes, de los 233 que pasaron a texto completo, que no tenían esos identificadores, y 2 que también habían pasado a texto completo y que la enmienda de idioma del 11 de agosto de 2026 excluyó después en la etapa de resumen.</t>
         </is>
       </c>
     </row>
@@ -703,7 +703,7 @@
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-19</t>
+          <t>Generado el 2026-10-20</t>
         </is>
       </c>
     </row>
